--- a/rules/CORE-000028/negative/01/data/unit-test-coreid-CG0008-negative.xlsx
+++ b/rules/CORE-000028/negative/01/data/unit-test-coreid-CG0008-negative.xlsx
@@ -1222,9 +1222,7 @@
       <c r="G5" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="H5" s="4" t="s">
-        <v>22</v>
-      </c>
+      <c r="H5" s="4"/>
       <c r="I5" s="2" t="s">
         <v>55</v>
       </c>
@@ -1251,9 +1249,7 @@
       <c r="G6" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="H6" s="4" t="s">
-        <v>22</v>
-      </c>
+      <c r="H6" s="4"/>
       <c r="I6" s="2" t="s">
         <v>55</v>
       </c>
@@ -1280,9 +1276,7 @@
       <c r="G7" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="H7" s="4" t="s">
-        <v>22</v>
-      </c>
+      <c r="H7" s="4"/>
       <c r="I7" s="2" t="s">
         <v>55</v>
       </c>
@@ -1453,9 +1447,7 @@
       <c r="H5" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="I5" s="4" t="s">
-        <v>22</v>
-      </c>
+      <c r="I5" s="4"/>
       <c r="J5" s="2" t="s">
         <v>55</v>
       </c>
@@ -1485,9 +1477,7 @@
       <c r="H6" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="I6" s="4" t="s">
-        <v>22</v>
-      </c>
+      <c r="I6" s="4"/>
       <c r="J6" s="2" t="s">
         <v>55</v>
       </c>
@@ -1517,9 +1507,7 @@
       <c r="H7" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="I7" s="4" t="s">
-        <v>22</v>
-      </c>
+      <c r="I7" s="4"/>
       <c r="J7" s="2" t="s">
         <v>55</v>
       </c>
